--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
   <si>
     <t>CODIGO</t>
   </si>
@@ -90,6 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -467,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -496,100 +497,326 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1357</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1357.0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1357.0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1357.0</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1771.62</v>
       </c>
-      <c r="G2">
-        <f>E2*F2</f>
-        <v>5314.86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1357</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="G4" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1357.0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1358.0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1358.0</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G5" si="0">E3*F3</f>
-        <v>8550.0400000000009</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1357</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1358.0</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>10687.550000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1357</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1358.0</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>12825.060000000001</v>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1359.0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1359.0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1359.0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1359.0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1360.0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1360.0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2137.51</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="16">
   <si>
     <t>CODIGO</t>
   </si>
@@ -468,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
@@ -819,6 +819,52 @@
         <v>2137.51</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1361.0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1361.0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EFDD01-AD33-451A-9074-E63CA1AACFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6969066-96AB-4820-A30F-1BABC7517B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{92F47CF0-95F9-4D84-814C-7AFFA20164B6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>CODIGO</t>
   </si>
@@ -90,7 +90,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -126,14 +125,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -497,78 +490,78 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1357.0</v>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1771.62</v>
+      </c>
+      <c r="G2">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1357.0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G3">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1357.0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1771.62</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1357.0</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G4">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -579,19 +572,19 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1358.0</v>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G5">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -602,19 +595,19 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>1771.62</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>1771.62</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1358.0</v>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -625,19 +618,19 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1358.0</v>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G7">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -648,19 +641,19 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1358.0</v>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G8">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -671,19 +664,19 @@
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1359.0</v>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G9">
+        <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -694,175 +687,37 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>1771.62</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1771.62</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1359.0</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
-      <c r="E11" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1359.0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1359.0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1360.0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1360.0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1361.0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1771.62</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1361.0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2137.51</v>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2137.5100000000002</v>
+      </c>
+      <c r="G11">
+        <v>2137.5100000000002</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
   <si>
     <t>CODIGO</t>
   </si>
@@ -84,12 +84,67 @@
   </si>
   <si>
     <t>Tóner original W2300A Magenta</t>
+  </si>
+  <si>
+    <t>CABL01</t>
+  </si>
+  <si>
+    <t>Cable HDMI 2 metros</t>
+  </si>
+  <si>
+    <t>HP1021</t>
+  </si>
+  <si>
+    <t>Papel bond tamaño oficio 75g</t>
+  </si>
+  <si>
+    <t>PAQ</t>
+  </si>
+  <si>
+    <t>REGU01</t>
+  </si>
+  <si>
+    <t>Regulador de voltaje 1000VA</t>
+  </si>
+  <si>
+    <t>EPSON01</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Negro</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>KEYB01</t>
+  </si>
+  <si>
+    <t>Teclado USB estándar Logitech</t>
+  </si>
+  <si>
+    <t>CAN002</t>
+  </si>
+  <si>
+    <t>Cartucho Canon PG-210 Negro</t>
+  </si>
+  <si>
+    <t>EPSON02</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Cian</t>
+  </si>
+  <si>
+    <t>USB002</t>
+  </si>
+  <si>
+    <t>Memoria USB 64GB Kingston</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -461,10 +516,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -718,6 +773,328 @@
       </c>
       <c r="G11">
         <v>2137.5100000000002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8550.04</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="G17" t="n">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>780.0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7165.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>310.0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>310.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>580.0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>580.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>180.0</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="36">
   <si>
     <t>CODIGO</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>Memoria USB 64GB Kingston</t>
+  </si>
+  <si>
+    <t>HP1020</t>
+  </si>
+  <si>
+    <t>Papel bond tamaño carta 75g</t>
   </si>
 </sst>
 </file>
@@ -516,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
@@ -1097,6 +1103,167 @@
         <v>180.0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>210.75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
   <si>
     <t>CODIGO</t>
   </si>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
@@ -850,144 +850,6 @@
         <v>2137.51</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>760.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8550.04</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>110.25</v>
-      </c>
-      <c r="G17" t="n">
-        <v>110.25</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>780.0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>210.75</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7165.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>310.0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>310.0</v>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" t="n">
         <v>6.0</v>
@@ -1262,6 +1124,144 @@
       </c>
       <c r="G32" t="n">
         <v>210.75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>760.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8550.04</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>110.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>780.0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7165.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>310.0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>310.0</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/INTORDENDECOMPRA.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="36">
   <si>
     <t>CODIGO</t>
   </si>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1658ADDC-DCFD-4FC0-A51D-94B360144F05}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.36328125" collapsed="true"/>
@@ -551,98 +551,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1771.62</v>
-      </c>
-      <c r="G2">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G3">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G4">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2137.5100000000002</v>
-      </c>
-      <c r="G5">
-        <v>2137.5100000000002</v>
-      </c>
-    </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
@@ -781,75 +689,6 @@
         <v>2137.5100000000002</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1771.62</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1771.62</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2137.51</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2137.51</v>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" t="n">
         <v>6.0</v>
@@ -1262,6 +1101,144 @@
       </c>
       <c r="G38" t="n">
         <v>310.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1771.62</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1771.62</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2137.51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2137.51</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2137.51</v>
       </c>
     </row>
   </sheetData>
